--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">privacy</t>
   </si>
   <si>
-    <t xml:space="preserve">video1.mp4</t>
+    <t xml:space="preserve">Movie 1.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 1</t>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Public</t>
   </si>
   <si>
-    <t xml:space="preserve">video2.mp4</t>
+    <t xml:space="preserve">Movie 2.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 1</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Brilliant Solo Goals</t>
   </si>
   <si>
-    <t xml:space="preserve">video3.mp4</t>
+    <t xml:space="preserve">Movie 3.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 1</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Midfield Masterclasses</t>
   </si>
   <si>
-    <t xml:space="preserve">video4.mp4</t>
+    <t xml:space="preserve">Movie 4.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 1</t>
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Goalkeeping Saves</t>
   </si>
   <si>
-    <t xml:space="preserve">video5.mp4</t>
+    <t xml:space="preserve">Movie 5.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 1</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Defensive Excellence</t>
   </si>
   <si>
-    <t xml:space="preserve">video6.mp4</t>
+    <t xml:space="preserve">Movie 6.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 1</t>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">Free Kick Magic</t>
   </si>
   <si>
-    <t xml:space="preserve">video7.mp4</t>
+    <t xml:space="preserve">Movie 7.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 1</t>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">Champions League Nights</t>
   </si>
   <si>
-    <t xml:space="preserve">video8.mp4</t>
+    <t xml:space="preserve">Movie 8.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 1</t>
@@ -169,7 +169,7 @@
     <t xml:space="preserve">World Cup Memories</t>
   </si>
   <si>
-    <t xml:space="preserve">video9.mp4</t>
+    <t xml:space="preserve">Movie 9.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 1</t>
@@ -184,7 +184,7 @@
     <t xml:space="preserve">Derby Rivalries</t>
   </si>
   <si>
-    <t xml:space="preserve">video10.mp4</t>
+    <t xml:space="preserve">Movie 10.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 1</t>
@@ -199,7 +199,7 @@
     <t xml:space="preserve">Attacking Football</t>
   </si>
   <si>
-    <t xml:space="preserve">video11.mp4</t>
+    <t xml:space="preserve">Movie 11.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 1</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video12.mp4</t>
+    <t xml:space="preserve">Movie 12.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 1</t>
@@ -223,7 +223,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video13.mp4</t>
+    <t xml:space="preserve">Movie 13.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 1</t>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video14.mp4</t>
+    <t xml:space="preserve">Movie 14.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 1</t>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video15.mp4</t>
+    <t xml:space="preserve">Movie 15.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 1</t>
@@ -259,7 +259,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video16.mp4</t>
+    <t xml:space="preserve">Movie 16.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 1</t>
@@ -271,7 +271,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video17.mp4</t>
+    <t xml:space="preserve">Movie 17.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 1</t>
@@ -283,7 +283,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video18.mp4</t>
+    <t xml:space="preserve">Movie 18.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 1</t>
@@ -295,7 +295,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video19.mp4</t>
+    <t xml:space="preserve">Movie 19.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 1</t>
@@ -307,7 +307,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video20.mp4</t>
+    <t xml:space="preserve">Movie 20.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 1</t>
@@ -319,7 +319,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-1</t>
   </si>
   <si>
-    <t xml:space="preserve">video21.mp4</t>
+    <t xml:space="preserve">Movie 21.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 2</t>
@@ -331,7 +331,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video22.mp4</t>
+    <t xml:space="preserve">Movie 22.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 2</t>
@@ -343,7 +343,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video23.mp4</t>
+    <t xml:space="preserve">Movie 23.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 2</t>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video24.mp4</t>
+    <t xml:space="preserve">Movie 24.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 2</t>
@@ -367,7 +367,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video25.mp4</t>
+    <t xml:space="preserve">Movie 25.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 2</t>
@@ -379,7 +379,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video26.mp4</t>
+    <t xml:space="preserve">Movie 26.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 2</t>
@@ -391,7 +391,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video27.mp4</t>
+    <t xml:space="preserve">Movie 27.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 2</t>
@@ -403,7 +403,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video28.mp4</t>
+    <t xml:space="preserve">Movie 28.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 2</t>
@@ -415,7 +415,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video29.mp4</t>
+    <t xml:space="preserve">Movie 29.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 2</t>
@@ -427,7 +427,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video30.mp4</t>
+    <t xml:space="preserve">Movie 30.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 2</t>
@@ -439,7 +439,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video31.mp4</t>
+    <t xml:space="preserve">Movie 31.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 2</t>
@@ -451,7 +451,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video32.mp4</t>
+    <t xml:space="preserve">Movie 32.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 2</t>
@@ -463,7 +463,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video33.mp4</t>
+    <t xml:space="preserve">Movie 33.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 2</t>
@@ -475,7 +475,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video34.mp4</t>
+    <t xml:space="preserve">Movie 34.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 2</t>
@@ -487,7 +487,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video35.mp4</t>
+    <t xml:space="preserve">Movie 35.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 2</t>
@@ -499,7 +499,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video36.mp4</t>
+    <t xml:space="preserve">Movie 36.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 2</t>
@@ -511,7 +511,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video37.mp4</t>
+    <t xml:space="preserve">Movie 37.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 2</t>
@@ -523,7 +523,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video38.mp4</t>
+    <t xml:space="preserve">Movie 38.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 2</t>
@@ -535,7 +535,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video39.mp4</t>
+    <t xml:space="preserve">Movie 39.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 2</t>
@@ -547,7 +547,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video40.mp4</t>
+    <t xml:space="preserve">Movie 40.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 2</t>
@@ -559,7 +559,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-2</t>
   </si>
   <si>
-    <t xml:space="preserve">video41.mp4</t>
+    <t xml:space="preserve">Movie 41.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 3</t>
@@ -571,7 +571,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video42.mp4</t>
+    <t xml:space="preserve">Movie 42.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 3</t>
@@ -583,7 +583,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video43.mp4</t>
+    <t xml:space="preserve">Movie 43.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 3</t>
@@ -595,7 +595,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video44.mp4</t>
+    <t xml:space="preserve">Movie 44.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 3</t>
@@ -607,7 +607,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video45.mp4</t>
+    <t xml:space="preserve">Movie 45.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 3</t>
@@ -619,7 +619,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video46.mp4</t>
+    <t xml:space="preserve">Movie 46.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 3</t>
@@ -631,7 +631,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video47.mp4</t>
+    <t xml:space="preserve">Movie 47.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 3</t>
@@ -643,7 +643,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video48.mp4</t>
+    <t xml:space="preserve">Movie 48.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 3</t>
@@ -655,7 +655,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video49.mp4</t>
+    <t xml:space="preserve">Movie 49.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 3</t>
@@ -667,7 +667,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video50.mp4</t>
+    <t xml:space="preserve">Movie 50.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 3</t>
@@ -679,7 +679,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video51.mp4</t>
+    <t xml:space="preserve">Movie 51.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 3</t>
@@ -691,7 +691,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video52.mp4</t>
+    <t xml:space="preserve">Movie 52.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 3</t>
@@ -703,7 +703,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video53.mp4</t>
+    <t xml:space="preserve">Movie 53.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 3</t>
@@ -715,7 +715,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video54.mp4</t>
+    <t xml:space="preserve">Movie 54.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 3</t>
@@ -727,7 +727,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video55.mp4</t>
+    <t xml:space="preserve">Movie 55.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 3</t>
@@ -739,7 +739,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video56.mp4</t>
+    <t xml:space="preserve">Movie 56.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 3</t>
@@ -751,7 +751,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video57.mp4</t>
+    <t xml:space="preserve">Movie 57.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 3</t>
@@ -763,7 +763,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video58.mp4</t>
+    <t xml:space="preserve">Movie 58.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 3</t>
@@ -775,7 +775,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video59.mp4</t>
+    <t xml:space="preserve">Movie 59.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 3</t>
@@ -787,7 +787,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video60.mp4</t>
+    <t xml:space="preserve">Movie 60.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 3</t>
@@ -799,7 +799,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-3</t>
   </si>
   <si>
-    <t xml:space="preserve">video61.mp4</t>
+    <t xml:space="preserve">Movie 61.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 4</t>
@@ -811,7 +811,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video62.mp4</t>
+    <t xml:space="preserve">Movie 62.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 4</t>
@@ -823,7 +823,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video63.mp4</t>
+    <t xml:space="preserve">Movie 63.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 4</t>
@@ -835,7 +835,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video64.mp4</t>
+    <t xml:space="preserve">Movie 64.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 4</t>
@@ -847,7 +847,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video65.mp4</t>
+    <t xml:space="preserve">Movie 65.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 4</t>
@@ -859,7 +859,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video66.mp4</t>
+    <t xml:space="preserve">Movie 66.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 4</t>
@@ -871,7 +871,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video67.mp4</t>
+    <t xml:space="preserve">Movie 67.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 4</t>
@@ -883,7 +883,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video68.mp4</t>
+    <t xml:space="preserve">Movie 68.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 4</t>
@@ -895,7 +895,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video69.mp4</t>
+    <t xml:space="preserve">Movie 69.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 4</t>
@@ -907,7 +907,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video70.mp4</t>
+    <t xml:space="preserve">Movie 70.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 4</t>
@@ -919,7 +919,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video71.mp4</t>
+    <t xml:space="preserve">Movie 71.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 4</t>
@@ -931,7 +931,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video72.mp4</t>
+    <t xml:space="preserve">Movie 72.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 4</t>
@@ -943,7 +943,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video73.mp4</t>
+    <t xml:space="preserve">Movie 73.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 4</t>
@@ -955,7 +955,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video74.mp4</t>
+    <t xml:space="preserve">Movie 74.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 4</t>
@@ -967,7 +967,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video75.mp4</t>
+    <t xml:space="preserve">Movie 75.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 4</t>
@@ -979,7 +979,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video76.mp4</t>
+    <t xml:space="preserve">Movie 76.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 4</t>
@@ -991,7 +991,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video77.mp4</t>
+    <t xml:space="preserve">Movie 77.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 4</t>
@@ -1003,7 +1003,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video78.mp4</t>
+    <t xml:space="preserve">Movie 78.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 4</t>
@@ -1015,7 +1015,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video79.mp4</t>
+    <t xml:space="preserve">Movie 79.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 4</t>
@@ -1027,7 +1027,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video80.mp4</t>
+    <t xml:space="preserve">Movie 80.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 4</t>
@@ -1039,7 +1039,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-4</t>
   </si>
   <si>
-    <t xml:space="preserve">video81.mp4</t>
+    <t xml:space="preserve">Movie 81.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 5</t>
@@ -1051,7 +1051,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video82.mp4</t>
+    <t xml:space="preserve">Movie 82.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 5</t>
@@ -1063,7 +1063,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video83.mp4</t>
+    <t xml:space="preserve">Movie 83.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 5</t>
@@ -1075,7 +1075,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video84.mp4</t>
+    <t xml:space="preserve">Movie 84.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 5</t>
@@ -1087,7 +1087,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video85.mp4</t>
+    <t xml:space="preserve">Movie 85.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 5</t>
@@ -1099,7 +1099,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video86.mp4</t>
+    <t xml:space="preserve">Movie 86.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 5</t>
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video87.mp4</t>
+    <t xml:space="preserve">Movie 87.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 5</t>
@@ -1123,7 +1123,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video88.mp4</t>
+    <t xml:space="preserve">Movie 88.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 5</t>
@@ -1135,7 +1135,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video89.mp4</t>
+    <t xml:space="preserve">Movie 89.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 5</t>
@@ -1147,7 +1147,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video90.mp4</t>
+    <t xml:space="preserve">Movie 90.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 5</t>
@@ -1159,7 +1159,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video91.mp4</t>
+    <t xml:space="preserve">Movie 91.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 5</t>
@@ -1171,7 +1171,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video92.mp4</t>
+    <t xml:space="preserve">Movie 92.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 5</t>
@@ -1183,7 +1183,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video93.mp4</t>
+    <t xml:space="preserve">Movie 93.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 5</t>
@@ -1195,7 +1195,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video94.mp4</t>
+    <t xml:space="preserve">Movie 94.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 5</t>
@@ -1207,7 +1207,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video95.mp4</t>
+    <t xml:space="preserve">Movie 95.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 5</t>
@@ -1219,7 +1219,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video96.mp4</t>
+    <t xml:space="preserve">Movie 96.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 5</t>
@@ -1231,7 +1231,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video97.mp4</t>
+    <t xml:space="preserve">Movie 97.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 5</t>
@@ -1243,7 +1243,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video98.mp4</t>
+    <t xml:space="preserve">Movie 98.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 5</t>
@@ -1255,7 +1255,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video99.mp4</t>
+    <t xml:space="preserve">Movie 99.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 5</t>
@@ -1267,7 +1267,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video100.mp4</t>
+    <t xml:space="preserve">Movie 100.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 5</t>
@@ -1279,7 +1279,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-5</t>
   </si>
   <si>
-    <t xml:space="preserve">video101.mp4</t>
+    <t xml:space="preserve">Movie 101.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 6</t>
@@ -1291,7 +1291,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video102.mp4</t>
+    <t xml:space="preserve">Movie 102.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 6</t>
@@ -1303,7 +1303,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video103.mp4</t>
+    <t xml:space="preserve">Movie 103.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 6</t>
@@ -1315,7 +1315,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video104.mp4</t>
+    <t xml:space="preserve">Movie 104.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 6</t>
@@ -1327,7 +1327,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video105.mp4</t>
+    <t xml:space="preserve">Movie 105.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 6</t>
@@ -1339,7 +1339,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video106.mp4</t>
+    <t xml:space="preserve">Movie 106.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 6</t>
@@ -1351,7 +1351,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video107.mp4</t>
+    <t xml:space="preserve">Movie 107.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 6</t>
@@ -1363,7 +1363,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video108.mp4</t>
+    <t xml:space="preserve">Movie 108.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 6</t>
@@ -1375,7 +1375,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video109.mp4</t>
+    <t xml:space="preserve">Movie 109.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 6</t>
@@ -1387,7 +1387,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video110.mp4</t>
+    <t xml:space="preserve">Movie 110.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 6</t>
@@ -1399,7 +1399,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video111.mp4</t>
+    <t xml:space="preserve">Movie 111.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 6</t>
@@ -1411,7 +1411,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video112.mp4</t>
+    <t xml:space="preserve">Movie 112.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 6</t>
@@ -1423,7 +1423,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video113.mp4</t>
+    <t xml:space="preserve">Movie 113.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 6</t>
@@ -1435,7 +1435,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video114.mp4</t>
+    <t xml:space="preserve">Movie 114.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 6</t>
@@ -1447,7 +1447,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video115.mp4</t>
+    <t xml:space="preserve">Movie 115.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 6</t>
@@ -1459,7 +1459,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video116.mp4</t>
+    <t xml:space="preserve">Movie 116.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 6</t>
@@ -1471,7 +1471,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video117.mp4</t>
+    <t xml:space="preserve">Movie 117.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 6</t>
@@ -1483,7 +1483,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video118.mp4</t>
+    <t xml:space="preserve">Movie 118.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 6</t>
@@ -1495,7 +1495,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video119.mp4</t>
+    <t xml:space="preserve">Movie 119.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 6</t>
@@ -1507,7 +1507,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video120.mp4</t>
+    <t xml:space="preserve">Movie 120.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 6</t>
@@ -1519,7 +1519,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-6</t>
   </si>
   <si>
-    <t xml:space="preserve">video121.mp4</t>
+    <t xml:space="preserve">Movie 121.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 7</t>
@@ -1531,7 +1531,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video122.mp4</t>
+    <t xml:space="preserve">Movie 122.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 7</t>
@@ -1543,7 +1543,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video123.mp4</t>
+    <t xml:space="preserve">Movie 123.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 7</t>
@@ -1555,7 +1555,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video124.mp4</t>
+    <t xml:space="preserve">Movie 124.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 7</t>
@@ -1567,7 +1567,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video125.mp4</t>
+    <t xml:space="preserve">Movie 125.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 7</t>
@@ -1579,7 +1579,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video126.mp4</t>
+    <t xml:space="preserve">Movie 126.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 7</t>
@@ -1591,7 +1591,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video127.mp4</t>
+    <t xml:space="preserve">Movie 127.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 7</t>
@@ -1603,7 +1603,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video128.mp4</t>
+    <t xml:space="preserve">Movie 128.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 7</t>
@@ -1615,7 +1615,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video129.mp4</t>
+    <t xml:space="preserve">Movie 129.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 7</t>
@@ -1627,7 +1627,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video130.mp4</t>
+    <t xml:space="preserve">Movie 130.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 7</t>
@@ -1639,7 +1639,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video131.mp4</t>
+    <t xml:space="preserve">Movie 131.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 7</t>
@@ -1651,7 +1651,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video132.mp4</t>
+    <t xml:space="preserve">Movie 132.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 7</t>
@@ -1663,7 +1663,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video133.mp4</t>
+    <t xml:space="preserve">Movie 133.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 7</t>
@@ -1675,7 +1675,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video134.mp4</t>
+    <t xml:space="preserve">Movie 134.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 7</t>
@@ -1687,7 +1687,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video135.mp4</t>
+    <t xml:space="preserve">Movie 135.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 7</t>
@@ -1699,7 +1699,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video136.mp4</t>
+    <t xml:space="preserve">Movie 136.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 7</t>
@@ -1711,7 +1711,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video137.mp4</t>
+    <t xml:space="preserve">Movie 137.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 7</t>
@@ -1723,7 +1723,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video138.mp4</t>
+    <t xml:space="preserve">Movie 138.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 7</t>
@@ -1735,7 +1735,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video139.mp4</t>
+    <t xml:space="preserve">Movie 139.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 7</t>
@@ -1747,7 +1747,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video140.mp4</t>
+    <t xml:space="preserve">Movie 140.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 7</t>
@@ -1759,7 +1759,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-7</t>
   </si>
   <si>
-    <t xml:space="preserve">video141.mp4</t>
+    <t xml:space="preserve">Movie 141.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 8</t>
@@ -1771,7 +1771,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video142.mp4</t>
+    <t xml:space="preserve">Movie 142.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 8</t>
@@ -1783,7 +1783,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,bravo-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video143.mp4</t>
+    <t xml:space="preserve">Movie 143.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Crimson 8</t>
@@ -1795,7 +1795,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,crimson-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video144.mp4</t>
+    <t xml:space="preserve">Movie 144.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Diamond 8</t>
@@ -1807,7 +1807,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,diamond-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video145.mp4</t>
+    <t xml:space="preserve">Movie 145.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Emerald 8</t>
@@ -1819,7 +1819,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,emerald-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video146.mp4</t>
+    <t xml:space="preserve">Movie 146.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Falcon 8</t>
@@ -1831,7 +1831,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,falcon-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video147.mp4</t>
+    <t xml:space="preserve">Movie 147.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Galaxy 8</t>
@@ -1843,7 +1843,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,galaxy-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video148.mp4</t>
+    <t xml:space="preserve">Movie 148.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Hero 8</t>
@@ -1855,7 +1855,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,hero-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video149.mp4</t>
+    <t xml:space="preserve">Movie 149.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Infinity 8</t>
@@ -1867,7 +1867,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,infinity-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video150.mp4</t>
+    <t xml:space="preserve">Movie 150.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Jubilee 8</t>
@@ -1879,7 +1879,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,jubilee-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video151.mp4</t>
+    <t xml:space="preserve">Movie 151.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Kingdom 8</t>
@@ -1891,7 +1891,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,kingdom-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video152.mp4</t>
+    <t xml:space="preserve">Movie 152.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Legacy 8</t>
@@ -1903,7 +1903,7 @@
     <t xml:space="preserve">football,solo goals,dribbling,finishing,skills,soccer,football highlights,match action,legacy-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video153.mp4</t>
+    <t xml:space="preserve">Movie 153.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Midfield Masterclasses Every True Football Supporter Should Experience Momentum 8</t>
@@ -1915,7 +1915,7 @@
     <t xml:space="preserve">football,midfield,playmaking,vision,passing,soccer,football highlights,match action,momentum-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video154.mp4</t>
+    <t xml:space="preserve">Movie 154.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Goalkeeping Saves Every True Football Supporter Should Experience Nova 8</t>
@@ -1927,7 +1927,7 @@
     <t xml:space="preserve">football,goalkeeper,saves,reflexes,clean sheets,soccer,football highlights,match action,nova-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video155.mp4</t>
+    <t xml:space="preserve">Movie 155.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Defensive Excellence Every True Football Supporter Should Experience Olympus 8</t>
@@ -1939,7 +1939,7 @@
     <t xml:space="preserve">football,defending,tackles,interceptions,defense,soccer,football highlights,match action,olympus-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video156.mp4</t>
+    <t xml:space="preserve">Movie 156.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Free Kick Magic Every True Football Supporter Should Experience Phoenix 8</t>
@@ -1951,7 +1951,7 @@
     <t xml:space="preserve">football,free kicks,set pieces,precision,goals,soccer,football highlights,match action,phoenix-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video157.mp4</t>
+    <t xml:space="preserve">Movie 157.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Champions League Nights Every True Football Supporter Should Experience Quantum 8</t>
@@ -1963,7 +1963,7 @@
     <t xml:space="preserve">football,champions league,europe,highlights,elite,soccer,football highlights,match action,quantum-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video158.mp4</t>
+    <t xml:space="preserve">Movie 158.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Memories Every True Football Supporter Should Experience Royal 8</t>
@@ -1975,7 +1975,7 @@
     <t xml:space="preserve">football,world cup,international,tournament,history,soccer,football highlights,match action,royal-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video159.mp4</t>
+    <t xml:space="preserve">Movie 159.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Derby Rivalries Every True Football Supporter Should Experience Summit 8</t>
@@ -1987,7 +1987,7 @@
     <t xml:space="preserve">football,derby,rivalry,passion,stadium,soccer,football highlights,match action,summit-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video160.mp4</t>
+    <t xml:space="preserve">Movie 160.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Attacking Football Every True Football Supporter Should Experience Titan 8</t>
@@ -1999,7 +1999,7 @@
     <t xml:space="preserve">football,attack,passing,goals,offense,soccer,football highlights,match action,titan-8</t>
   </si>
   <si>
-    <t xml:space="preserve">video161.mp4</t>
+    <t xml:space="preserve">Movie 161.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Greatest Comebacks Every True Football Supporter Should Experience Alpha 9</t>
@@ -2011,7 +2011,7 @@
     <t xml:space="preserve">football,comeback,soccer,epic matches,resilience,teamwork,football highlights,match action,alpha-9</t>
   </si>
   <si>
-    <t xml:space="preserve">video162.mp4</t>
+    <t xml:space="preserve">Movie 162.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Brilliant Solo Goals Every True Football Supporter Should Experience Bravo 9</t>
@@ -2035,6 +2035,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2094,8 +2095,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2225,3761 +2230,3761 @@
   <dimension ref="A1:G163"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="71.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="239.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="84.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="71.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="239.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="84.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="0" t="s">
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="0" t="s">
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="0" t="s">
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="0" t="s">
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="0" t="s">
+      <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="0" t="s">
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="0" t="s">
+      <c r="E12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="0" t="s">
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="0" t="s">
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="0" t="s">
+      <c r="E15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="0" t="s">
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="0" t="s">
+      <c r="E17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="0" t="s">
+      <c r="E18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="0" t="s">
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="0" t="s">
+      <c r="E20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="0" t="s">
+      <c r="E21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="0" t="s">
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="0" t="s">
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="0" t="s">
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="0" t="s">
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="G25" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="0" t="s">
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="0" t="s">
+      <c r="E27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="G27" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="0" t="s">
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="G28" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="0" t="s">
+      <c r="E29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="G29" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E30" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="0" t="s">
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="G30" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E31" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="0" t="s">
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="G31" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E32" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="0" t="s">
+      <c r="E32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="0" t="s">
+      <c r="G32" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="0" t="s">
+      <c r="E33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E34" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="0" t="s">
+      <c r="E34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="0" t="s">
+      <c r="G34" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E35" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="0" t="s">
+      <c r="E35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="G35" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="0" t="s">
+      <c r="E36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E37" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="0" t="s">
+      <c r="E37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="0" t="s">
+      <c r="E38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E39" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="0" t="s">
+      <c r="E39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E40" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="0" t="s">
+      <c r="E40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E41" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="0" t="s">
+      <c r="E41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="G41" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E42" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="0" t="s">
+      <c r="E42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E43" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="0" t="s">
+      <c r="E43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E44" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="0" t="s">
+      <c r="E44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E45" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="0" t="s">
+      <c r="E45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="G45" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="0" t="s">
+      <c r="E46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E47" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="0" t="s">
+      <c r="E47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E48" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="0" t="s">
+      <c r="E48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E49" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="0" t="s">
+      <c r="E49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E50" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="0" t="s">
+      <c r="E50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="G50" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E51" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="0" t="s">
+      <c r="E51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E52" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="0" t="s">
+      <c r="E52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E53" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="0" t="s">
+      <c r="E53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="0" t="s">
+      <c r="G53" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E54" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="0" t="s">
+      <c r="E54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="G54" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E55" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="0" t="s">
+      <c r="E55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G55" s="0" t="s">
+      <c r="G55" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C56" s="0" t="s">
+      <c r="C56" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E56" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="0" t="s">
+      <c r="E56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G56" s="0" t="s">
+      <c r="G56" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C57" s="0" t="s">
+      <c r="C57" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E57" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="0" t="s">
+      <c r="E57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G57" s="0" t="s">
+      <c r="G57" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="C58" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E58" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="0" t="s">
+      <c r="E58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G58" s="0" t="s">
+      <c r="G58" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E59" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="0" t="s">
+      <c r="E59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G59" s="0" t="s">
+      <c r="G59" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E60" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="0" t="s">
+      <c r="E60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G60" s="0" t="s">
+      <c r="G60" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E61" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="0" t="s">
+      <c r="E61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G61" s="0" t="s">
+      <c r="G61" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E62" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="0" t="s">
+      <c r="E62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="G62" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E63" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="0" t="s">
+      <c r="E63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G63" s="0" t="s">
+      <c r="G63" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E64" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="0" t="s">
+      <c r="E64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G64" s="0" t="s">
+      <c r="G64" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C65" s="0" t="s">
+      <c r="C65" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E65" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="0" t="s">
+      <c r="E65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G65" s="0" t="s">
+      <c r="G65" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E66" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="0" t="s">
+      <c r="E66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="G66" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E67" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="0" t="s">
+      <c r="E67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G67" s="0" t="s">
+      <c r="G67" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E68" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="0" t="s">
+      <c r="E68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="G68" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E69" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="0" t="s">
+      <c r="E69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G69" s="0" t="s">
+      <c r="G69" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E70" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="0" t="s">
+      <c r="E70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="G70" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C71" s="0" t="s">
+      <c r="C71" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E71" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="0" t="s">
+      <c r="E71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G71" s="0" t="s">
+      <c r="G71" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="C72" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E72" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="0" t="s">
+      <c r="E72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="0" t="s">
+      <c r="G72" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C73" s="0" t="s">
+      <c r="C73" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E73" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="0" t="s">
+      <c r="E73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="G73" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C74" s="0" t="s">
+      <c r="C74" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E74" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="0" t="s">
+      <c r="E74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="G74" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C75" s="0" t="s">
+      <c r="C75" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E75" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="0" t="s">
+      <c r="E75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="G75" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C76" s="0" t="s">
+      <c r="C76" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E76" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="0" t="s">
+      <c r="E76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="G76" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C77" s="0" t="s">
+      <c r="C77" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E77" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" s="0" t="s">
+      <c r="E77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G77" s="0" t="s">
+      <c r="G77" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C78" s="0" t="s">
+      <c r="C78" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="D78" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E78" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="0" t="s">
+      <c r="E78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="G78" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C79" s="0" t="s">
+      <c r="C79" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="D79" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E79" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" s="0" t="s">
+      <c r="E79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G79" s="0" t="s">
+      <c r="G79" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C80" s="0" t="s">
+      <c r="C80" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="D80" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E80" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" s="0" t="s">
+      <c r="E80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G80" s="0" t="s">
+      <c r="G80" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C81" s="0" t="s">
+      <c r="C81" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E81" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" s="0" t="s">
+      <c r="E81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="G81" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C82" s="0" t="s">
+      <c r="C82" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E82" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" s="0" t="s">
+      <c r="E82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="0" t="s">
+      <c r="G82" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C83" s="0" t="s">
+      <c r="C83" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E83" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="0" t="s">
+      <c r="E83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="G83" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C84" s="0" t="s">
+      <c r="C84" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="D84" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E84" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="0" t="s">
+      <c r="E84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="G84" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="0" t="s">
+      <c r="C85" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E85" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="0" t="s">
+      <c r="E85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G85" s="0" t="s">
+      <c r="G85" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C86" s="0" t="s">
+      <c r="C86" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="E86" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" s="0" t="s">
+      <c r="E86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="G86" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C87" s="0" t="s">
+      <c r="C87" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="D87" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E87" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F87" s="0" t="s">
+      <c r="E87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G87" s="0" t="s">
+      <c r="G87" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C88" s="0" t="s">
+      <c r="C88" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="D88" s="0" t="s">
+      <c r="D88" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E88" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="0" t="s">
+      <c r="E88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G88" s="0" t="s">
+      <c r="G88" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C89" s="0" t="s">
+      <c r="C89" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D89" s="0" t="s">
+      <c r="D89" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E89" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" s="0" t="s">
+      <c r="E89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G89" s="0" t="s">
+      <c r="G89" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C90" s="0" t="s">
+      <c r="C90" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D90" s="0" t="s">
+      <c r="D90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="E90" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" s="0" t="s">
+      <c r="E90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="G90" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C91" s="0" t="s">
+      <c r="C91" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D91" s="0" t="s">
+      <c r="D91" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E91" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="0" t="s">
+      <c r="E91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G91" s="0" t="s">
+      <c r="G91" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C92" s="0" t="s">
+      <c r="C92" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D92" s="0" t="s">
+      <c r="D92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E92" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="0" t="s">
+      <c r="E92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="0" t="s">
+      <c r="G92" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C93" s="0" t="s">
+      <c r="C93" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D93" s="0" t="s">
+      <c r="D93" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="E93" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" s="0" t="s">
+      <c r="E93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G93" s="0" t="s">
+      <c r="G93" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C94" s="0" t="s">
+      <c r="C94" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D94" s="0" t="s">
+      <c r="D94" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E94" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" s="0" t="s">
+      <c r="E94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G94" s="0" t="s">
+      <c r="G94" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C95" s="0" t="s">
+      <c r="C95" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D95" s="0" t="s">
+      <c r="D95" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E95" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" s="0" t="s">
+      <c r="E95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G95" s="0" t="s">
+      <c r="G95" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C96" s="0" t="s">
+      <c r="C96" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D96" s="0" t="s">
+      <c r="D96" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="E96" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" s="0" t="s">
+      <c r="E96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G96" s="0" t="s">
+      <c r="G96" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C97" s="0" t="s">
+      <c r="C97" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D97" s="0" t="s">
+      <c r="D97" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E97" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" s="0" t="s">
+      <c r="E97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G97" s="0" t="s">
+      <c r="G97" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C98" s="0" t="s">
+      <c r="C98" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D98" s="0" t="s">
+      <c r="D98" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E98" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" s="0" t="s">
+      <c r="E98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G98" s="0" t="s">
+      <c r="G98" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="0" t="s">
+      <c r="C99" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D99" s="0" t="s">
+      <c r="D99" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="E99" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="0" t="s">
+      <c r="E99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="G99" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C100" s="0" t="s">
+      <c r="C100" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D100" s="0" t="s">
+      <c r="D100" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E100" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" s="0" t="s">
+      <c r="E100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="G100" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C101" s="0" t="s">
+      <c r="C101" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D101" s="0" t="s">
+      <c r="D101" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E101" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" s="0" t="s">
+      <c r="E101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="G101" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C102" s="0" t="s">
+      <c r="C102" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="D102" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E102" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" s="0" t="s">
+      <c r="E102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="0" t="s">
+      <c r="G102" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C103" s="0" t="s">
+      <c r="C103" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="D103" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E103" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="0" t="s">
+      <c r="E103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="G103" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C104" s="0" t="s">
+      <c r="C104" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D104" s="0" t="s">
+      <c r="D104" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E104" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" s="0" t="s">
+      <c r="E104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G104" s="0" t="s">
+      <c r="G104" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C105" s="0" t="s">
+      <c r="C105" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D105" s="0" t="s">
+      <c r="D105" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E105" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" s="0" t="s">
+      <c r="E105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="G105" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C106" s="0" t="s">
+      <c r="C106" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D106" s="0" t="s">
+      <c r="D106" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="E106" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="0" t="s">
+      <c r="E106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="G106" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C107" s="0" t="s">
+      <c r="C107" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D107" s="0" t="s">
+      <c r="D107" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E107" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="0" t="s">
+      <c r="E107" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G107" s="0" t="s">
+      <c r="G107" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C108" s="0" t="s">
+      <c r="C108" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D108" s="0" t="s">
+      <c r="D108" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="E108" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="0" t="s">
+      <c r="E108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G108" s="0" t="s">
+      <c r="G108" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C109" s="0" t="s">
+      <c r="C109" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D109" s="0" t="s">
+      <c r="D109" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E109" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" s="0" t="s">
+      <c r="E109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G109" s="0" t="s">
+      <c r="G109" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C110" s="0" t="s">
+      <c r="C110" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="D110" s="0" t="s">
+      <c r="D110" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="E110" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" s="0" t="s">
+      <c r="E110" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G110" s="0" t="s">
+      <c r="G110" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C111" s="0" t="s">
+      <c r="C111" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D111" s="0" t="s">
+      <c r="D111" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="E111" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" s="0" t="s">
+      <c r="E111" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G111" s="0" t="s">
+      <c r="G111" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C112" s="0" t="s">
+      <c r="C112" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D112" s="0" t="s">
+      <c r="D112" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E112" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="0" t="s">
+      <c r="E112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="0" t="s">
+      <c r="G112" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C113" s="0" t="s">
+      <c r="C113" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D113" s="0" t="s">
+      <c r="D113" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="E113" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" s="0" t="s">
+      <c r="E113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G113" s="0" t="s">
+      <c r="G113" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C114" s="0" t="s">
+      <c r="C114" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D114" s="0" t="s">
+      <c r="D114" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="E114" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" s="0" t="s">
+      <c r="E114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G114" s="0" t="s">
+      <c r="G114" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C115" s="0" t="s">
+      <c r="C115" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D115" s="0" t="s">
+      <c r="D115" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E115" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" s="0" t="s">
+      <c r="E115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G115" s="0" t="s">
+      <c r="G115" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C116" s="0" t="s">
+      <c r="C116" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D116" s="0" t="s">
+      <c r="D116" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E116" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="0" t="s">
+      <c r="E116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G116" s="0" t="s">
+      <c r="G116" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C117" s="0" t="s">
+      <c r="C117" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D117" s="0" t="s">
+      <c r="D117" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="E117" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F117" s="0" t="s">
+      <c r="E117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G117" s="0" t="s">
+      <c r="G117" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C118" s="0" t="s">
+      <c r="C118" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D118" s="0" t="s">
+      <c r="D118" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E118" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="0" t="s">
+      <c r="E118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G118" s="0" t="s">
+      <c r="G118" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C119" s="0" t="s">
+      <c r="C119" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D119" s="0" t="s">
+      <c r="D119" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="E119" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F119" s="0" t="s">
+      <c r="E119" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G119" s="0" t="s">
+      <c r="G119" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C120" s="0" t="s">
+      <c r="C120" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D120" s="0" t="s">
+      <c r="D120" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="E120" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" s="0" t="s">
+      <c r="E120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G120" s="0" t="s">
+      <c r="G120" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C121" s="0" t="s">
+      <c r="C121" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D121" s="0" t="s">
+      <c r="D121" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="E121" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F121" s="0" t="s">
+      <c r="E121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G121" s="0" t="s">
+      <c r="G121" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C122" s="0" t="s">
+      <c r="C122" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D122" s="0" t="s">
+      <c r="D122" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="E122" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" s="0" t="s">
+      <c r="E122" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="0" t="s">
+      <c r="G122" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C123" s="0" t="s">
+      <c r="C123" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D123" s="0" t="s">
+      <c r="D123" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="E123" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="0" t="s">
+      <c r="E123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G123" s="0" t="s">
+      <c r="G123" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C124" s="0" t="s">
+      <c r="C124" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D124" s="0" t="s">
+      <c r="D124" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E124" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F124" s="0" t="s">
+      <c r="E124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G124" s="0" t="s">
+      <c r="G124" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C125" s="0" t="s">
+      <c r="C125" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D125" s="0" t="s">
+      <c r="D125" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="E125" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" s="0" t="s">
+      <c r="E125" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G125" s="0" t="s">
+      <c r="G125" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C126" s="0" t="s">
+      <c r="C126" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D126" s="0" t="s">
+      <c r="D126" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E126" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" s="0" t="s">
+      <c r="E126" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G126" s="0" t="s">
+      <c r="G126" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="0" t="s">
+      <c r="C127" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D127" s="0" t="s">
+      <c r="D127" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E127" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" s="0" t="s">
+      <c r="E127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G127" s="0" t="s">
+      <c r="G127" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C128" s="0" t="s">
+      <c r="C128" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D128" s="0" t="s">
+      <c r="D128" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="E128" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" s="0" t="s">
+      <c r="E128" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G128" s="0" t="s">
+      <c r="G128" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C129" s="0" t="s">
+      <c r="C129" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D129" s="0" t="s">
+      <c r="D129" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="E129" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" s="0" t="s">
+      <c r="E129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G129" s="0" t="s">
+      <c r="G129" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C130" s="0" t="s">
+      <c r="C130" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D130" s="0" t="s">
+      <c r="D130" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="E130" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" s="0" t="s">
+      <c r="E130" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G130" s="0" t="s">
+      <c r="G130" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C131" s="0" t="s">
+      <c r="C131" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D131" s="0" t="s">
+      <c r="D131" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E131" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" s="0" t="s">
+      <c r="E131" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G131" s="0" t="s">
+      <c r="G131" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C132" s="0" t="s">
+      <c r="C132" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D132" s="0" t="s">
+      <c r="D132" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="E132" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="0" t="s">
+      <c r="E132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G132" s="0" t="s">
+      <c r="G132" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C133" s="0" t="s">
+      <c r="C133" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D133" s="0" t="s">
+      <c r="D133" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E133" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="0" t="s">
+      <c r="E133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G133" s="0" t="s">
+      <c r="G133" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C134" s="0" t="s">
+      <c r="C134" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D134" s="0" t="s">
+      <c r="D134" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="E134" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" s="0" t="s">
+      <c r="E134" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G134" s="0" t="s">
+      <c r="G134" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D135" s="0" t="s">
+      <c r="D135" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="E135" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F135" s="0" t="s">
+      <c r="E135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G135" s="0" t="s">
+      <c r="G135" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C136" s="0" t="s">
+      <c r="C136" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D136" s="0" t="s">
+      <c r="D136" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="E136" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="0" t="s">
+      <c r="E136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G136" s="0" t="s">
+      <c r="G136" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+      <c r="A137" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C137" s="0" t="s">
+      <c r="C137" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D137" s="0" t="s">
+      <c r="D137" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E137" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="0" t="s">
+      <c r="E137" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G137" s="0" t="s">
+      <c r="G137" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+      <c r="A138" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C138" s="0" t="s">
+      <c r="C138" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="D138" s="0" t="s">
+      <c r="D138" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="E138" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F138" s="0" t="s">
+      <c r="E138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G138" s="0" t="s">
+      <c r="G138" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+      <c r="A139" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C139" s="0" t="s">
+      <c r="C139" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="D139" s="0" t="s">
+      <c r="D139" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="E139" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F139" s="0" t="s">
+      <c r="E139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G139" s="0" t="s">
+      <c r="G139" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+      <c r="A140" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C140" s="0" t="s">
+      <c r="C140" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D140" s="0" t="s">
+      <c r="D140" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="E140" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" s="0" t="s">
+      <c r="E140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G140" s="0" t="s">
+      <c r="G140" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="s">
+      <c r="A141" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C141" s="0" t="s">
+      <c r="C141" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D141" s="0" t="s">
+      <c r="D141" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E141" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="0" t="s">
+      <c r="E141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G141" s="0" t="s">
+      <c r="G141" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="s">
+      <c r="A142" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="C142" s="0" t="s">
+      <c r="C142" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="D142" s="0" t="s">
+      <c r="D142" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E142" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F142" s="0" t="s">
+      <c r="E142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G142" s="0" t="s">
+      <c r="G142" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
+      <c r="A143" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C143" s="0" t="s">
+      <c r="C143" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="D143" s="0" t="s">
+      <c r="D143" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="E143" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F143" s="0" t="s">
+      <c r="E143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G143" s="0" t="s">
+      <c r="G143" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="s">
+      <c r="A144" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C144" s="0" t="s">
+      <c r="C144" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="D144" s="0" t="s">
+      <c r="D144" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="E144" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" s="0" t="s">
+      <c r="E144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G144" s="0" t="s">
+      <c r="G144" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="s">
+      <c r="A145" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C145" s="0" t="s">
+      <c r="C145" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="D145" s="0" t="s">
+      <c r="D145" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="E145" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="0" t="s">
+      <c r="E145" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G145" s="0" t="s">
+      <c r="G145" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
+      <c r="A146" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="C146" s="0" t="s">
+      <c r="C146" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="D146" s="0" t="s">
+      <c r="D146" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="E146" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" s="0" t="s">
+      <c r="E146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G146" s="0" t="s">
+      <c r="G146" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="s">
+      <c r="A147" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="C147" s="0" t="s">
+      <c r="C147" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="D147" s="0" t="s">
+      <c r="D147" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="E147" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="0" t="s">
+      <c r="E147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G147" s="0" t="s">
+      <c r="G147" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
+      <c r="A148" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="C148" s="0" t="s">
+      <c r="C148" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="D148" s="0" t="s">
+      <c r="D148" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="E148" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="0" t="s">
+      <c r="E148" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G148" s="0" t="s">
+      <c r="G148" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
+      <c r="A149" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="C149" s="0" t="s">
+      <c r="C149" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="D149" s="0" t="s">
+      <c r="D149" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="E149" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F149" s="0" t="s">
+      <c r="E149" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G149" s="0" t="s">
+      <c r="G149" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="s">
+      <c r="A150" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B150" s="0" t="s">
+      <c r="B150" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="C150" s="0" t="s">
+      <c r="C150" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="D150" s="0" t="s">
+      <c r="D150" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="E150" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F150" s="0" t="s">
+      <c r="E150" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G150" s="0" t="s">
+      <c r="G150" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="s">
+      <c r="A151" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B151" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="C151" s="0" t="s">
+      <c r="C151" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="D151" s="0" t="s">
+      <c r="D151" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="E151" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F151" s="0" t="s">
+      <c r="E151" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G151" s="0" t="s">
+      <c r="G151" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="s">
+      <c r="A152" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B152" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="C152" s="0" t="s">
+      <c r="C152" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="D152" s="0" t="s">
+      <c r="D152" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="E152" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F152" s="0" t="s">
+      <c r="E152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G152" s="0" t="s">
+      <c r="G152" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="s">
+      <c r="A153" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B153" s="0" t="s">
+      <c r="B153" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="C153" s="0" t="s">
+      <c r="C153" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="D153" s="0" t="s">
+      <c r="D153" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="E153" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F153" s="0" t="s">
+      <c r="E153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G153" s="0" t="s">
+      <c r="G153" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="s">
+      <c r="A154" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B154" s="0" t="s">
+      <c r="B154" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="C154" s="0" t="s">
+      <c r="C154" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="D154" s="0" t="s">
+      <c r="D154" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="E154" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F154" s="0" t="s">
+      <c r="E154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G154" s="0" t="s">
+      <c r="G154" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="s">
+      <c r="A155" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="B155" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="C155" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D155" s="0" t="s">
+      <c r="D155" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E155" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F155" s="0" t="s">
+      <c r="E155" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G155" s="0" t="s">
+      <c r="G155" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="s">
+      <c r="A156" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B156" s="0" t="s">
+      <c r="B156" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C156" s="0" t="s">
+      <c r="C156" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="D156" s="0" t="s">
+      <c r="D156" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="E156" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F156" s="0" t="s">
+      <c r="E156" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G156" s="0" t="s">
+      <c r="G156" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="s">
+      <c r="A157" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="B157" s="0" t="s">
+      <c r="B157" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="C157" s="0" t="s">
+      <c r="C157" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="D157" s="0" t="s">
+      <c r="D157" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E157" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F157" s="0" t="s">
+      <c r="E157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G157" s="0" t="s">
+      <c r="G157" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
+      <c r="A158" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B158" s="0" t="s">
+      <c r="B158" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C158" s="0" t="s">
+      <c r="C158" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D158" s="0" t="s">
+      <c r="D158" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="E158" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F158" s="0" t="s">
+      <c r="E158" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G158" s="0" t="s">
+      <c r="G158" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="s">
+      <c r="A159" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B159" s="0" t="s">
+      <c r="B159" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C159" s="0" t="s">
+      <c r="C159" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="D159" s="0" t="s">
+      <c r="D159" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="E159" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F159" s="0" t="s">
+      <c r="E159" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G159" s="0" t="s">
+      <c r="G159" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="s">
+      <c r="A160" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B160" s="0" t="s">
+      <c r="B160" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="C160" s="0" t="s">
+      <c r="C160" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D160" s="0" t="s">
+      <c r="D160" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="E160" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F160" s="0" t="s">
+      <c r="E160" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G160" s="0" t="s">
+      <c r="G160" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
+      <c r="A161" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B161" s="0" t="s">
+      <c r="B161" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C161" s="0" t="s">
+      <c r="C161" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="D161" s="0" t="s">
+      <c r="D161" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="E161" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" s="0" t="s">
+      <c r="E161" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G161" s="0" t="s">
+      <c r="G161" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="s">
+      <c r="A162" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B162" s="0" t="s">
+      <c r="B162" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="C162" s="0" t="s">
+      <c r="C162" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="D162" s="0" t="s">
+      <c r="D162" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="E162" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F162" s="0" t="s">
+      <c r="E162" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G162" s="0" t="s">
+      <c r="G162" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="s">
+      <c r="A163" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B163" s="0" t="s">
+      <c r="B163" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C163" s="0" t="s">
+      <c r="C163" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D163" s="0" t="s">
+      <c r="D163" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="E163" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F163" s="0" t="s">
+      <c r="E163" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G163" s="0" t="s">
+      <c r="G163" s="1" t="s">
         <v>13</v>
       </c>
     </row>
